--- a/artfynd/S 723-2023 artfynd.xlsx
+++ b/artfynd/S 723-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101313898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101313915</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271862</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17269522</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17269549</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53065697</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53065699</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101313749</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101313817</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101313838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,8 +2023,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101313859</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>